--- a/Entendimento dos dados/Tabelas_Selecionadas.xlsx
+++ b/Entendimento dos dados/Tabelas_Selecionadas.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Viery2\tcc_aplicacao\Entendimento dos dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\tcc_aplicacao\Entendimento dos dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FD94D5-E5B7-428B-9B53-0665554C6098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08108213-1760-4FBC-B599-ACCF2660F71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4665" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{0228065A-DD01-4A31-BC54-03B71CE945F9}"/>
+    <workbookView xWindow="28680" yWindow="-4665" windowWidth="29040" windowHeight="15720" xr2:uid="{0228065A-DD01-4A31-BC54-03B71CE945F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Variáveis" sheetId="1" r:id="rId1"/>
-    <sheet name="IOT" sheetId="3" r:id="rId2"/>
-    <sheet name="Robos" sheetId="5" r:id="rId3"/>
-    <sheet name="Bigdata" sheetId="7" r:id="rId4"/>
-    <sheet name="IA tipo" sheetId="8" r:id="rId5"/>
-    <sheet name="IA aplicação" sheetId="9" r:id="rId6"/>
-    <sheet name="NÃO IA" sheetId="10" r:id="rId7"/>
+    <sheet name="Planilha2" sheetId="12" r:id="rId2"/>
+    <sheet name="A1A" sheetId="11" r:id="rId3"/>
+    <sheet name="IOT" sheetId="3" r:id="rId4"/>
+    <sheet name="Robos" sheetId="5" r:id="rId5"/>
+    <sheet name="Bigdata" sheetId="7" r:id="rId6"/>
+    <sheet name="IA tipo" sheetId="8" r:id="rId7"/>
+    <sheet name="IA aplicação" sheetId="9" r:id="rId8"/>
+    <sheet name="NÃO IA" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Variáveis!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Variáveis!$A$1:$J$23</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="144">
   <si>
     <t>Tabela</t>
   </si>
@@ -418,6 +420,87 @@
   <si>
     <t>Não enxergam utilidade</t>
   </si>
+  <si>
+    <t>A1A - EMPRESAS EM QUE HÁ UMA ÁREA OU DEPARTAMENTO DE TI</t>
+  </si>
+  <si>
+    <t>A1A</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Não sabe</t>
+  </si>
+  <si>
+    <t>Não respondeu</t>
+  </si>
+  <si>
+    <t>Questão</t>
+  </si>
+  <si>
+    <t>Variaveis</t>
+  </si>
+  <si>
+    <t>H3 - Empresas fazem uso de robôs indutriais</t>
+  </si>
+  <si>
+    <t>H3B - Que fazem uso de robôs de serviço</t>
+  </si>
+  <si>
+    <t>A1A - Empresas em que há uam área ou departamento de TI</t>
+  </si>
+  <si>
+    <t>G2 - Empresas que utilizaram pacotes de software ERP</t>
+  </si>
+  <si>
+    <t>G3 - Empresas que utilizaram pacotes de software para CRM</t>
+  </si>
+  <si>
+    <t>B18 - Empresas que pagaram por Serviços de Nuvem</t>
+  </si>
+  <si>
+    <t>E1 - Empresas que compraram pela internet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2 - Empresas que venderam pela internet </t>
+  </si>
+  <si>
+    <t>HA1 - Empresas que fazem análise de Big Data</t>
+  </si>
+  <si>
+    <t>H4B - Empresas que fazem uso de impressão 3D</t>
+  </si>
+  <si>
+    <t>H8 - Empresas que utilizaram dispositivos inteligentes ou Internet das Coisas</t>
+  </si>
+  <si>
+    <t>H9A - Empresas que utilizaram Inteligência Artificial por tipo de tecnologia</t>
+  </si>
+  <si>
+    <t>H10 - Empresas que utilizaram Inteligência Artifical por tipo de aplicação</t>
+  </si>
+  <si>
+    <t>H13 - Empresas que não utilizaram IA por algum típo de obstáculo</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>sim / não</t>
+  </si>
+  <si>
+    <t>qualificadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -427,7 +510,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,11 +572,13 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -549,6 +634,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF6C757D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -593,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -634,12 +731,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -746,6 +863,32 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -761,6 +904,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8856,7 +9014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73FF5B2A-63CC-45FC-B2E7-CE4A9AE78A38}">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="149.6640625" style="1" customWidth="1"/>
@@ -8867,27 +9025,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="43" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="57" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
+      <c r="A2" s="54"/>
       <c r="B2" s="12">
         <v>2014</v>
       </c>
@@ -8909,47 +9067,28 @@
       <c r="H2" s="13">
         <v>2024</v>
       </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="46"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
+      <c r="A3" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J4" t="s">
@@ -8958,16 +9097,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="11" t="s">
+      <c r="E5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>19</v>
       </c>
       <c r="J5" t="s">
@@ -8976,7 +9123,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -8993,23 +9140,26 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="6"/>
+      <c r="A7" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="6"/>
@@ -9024,7 +9174,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="6"/>
@@ -9039,7 +9189,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -9054,12 +9204,12 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -9068,49 +9218,49 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>88</v>
+      <c r="A12" s="15" t="s">
+        <v>27</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="5">
-        <v>34</v>
-      </c>
-      <c r="F12" s="5">
-        <v>39</v>
-      </c>
-      <c r="G12" s="5">
-        <v>47</v>
-      </c>
-      <c r="H12" s="5">
-        <v>52</v>
-      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
-        <v>6</v>
+      <c r="A13" s="35" t="s">
+        <v>88</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="E13" s="5">
+        <v>34</v>
+      </c>
+      <c r="F13" s="5">
+        <v>39</v>
+      </c>
+      <c r="G13" s="5">
+        <v>47</v>
+      </c>
+      <c r="H13" s="5">
+        <v>52</v>
+      </c>
       <c r="I13" s="11" t="s">
         <v>19</v>
       </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="38" t="s">
-        <v>89</v>
+      <c r="A14" s="37" t="s">
+        <v>6</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="6"/>
@@ -9122,13 +9272,10 @@
       <c r="I14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J14" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
-        <v>7</v>
+      <c r="A15" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -9138,15 +9285,15 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="33" t="s">
-        <v>9</v>
+      <c r="A16" s="39" t="s">
+        <v>7</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
@@ -9156,17 +9303,20 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -9175,8 +9325,8 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
-        <v>11</v>
+      <c r="A18" s="33" t="s">
+        <v>10</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
@@ -9186,12 +9336,12 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="33" t="s">
-        <v>12</v>
+      <c r="A19" s="36" t="s">
+        <v>11</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
@@ -9201,12 +9351,12 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="32" t="s">
-        <v>13</v>
+      <c r="A20" s="33" t="s">
+        <v>12</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
@@ -9216,50 +9366,56 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
+    <row r="22" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="30" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
@@ -9316,6 +9472,9 @@
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="43" t="s">
+        <v>117</v>
+      </c>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -9486,8 +9645,17 @@
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
     </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" s="7"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J22" xr:uid="{73FF5B2A-63CC-45FC-B2E7-CE4A9AE78A38}">
+  <autoFilter ref="A1:J23" xr:uid="{73FF5B2A-63CC-45FC-B2E7-CE4A9AE78A38}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="2" showButton="0"/>
     <filterColumn colId="3" showButton="0"/>
@@ -9507,6 +9675,609 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0284680-EE7D-4ACD-AF6B-8B95745644F7}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.109375" style="47" customWidth="1"/>
+    <col min="2" max="8" width="6" style="47" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="63"/>
+      <c r="B2" s="49">
+        <v>2014</v>
+      </c>
+      <c r="C2" s="49">
+        <v>2015</v>
+      </c>
+      <c r="D2" s="49">
+        <v>2017</v>
+      </c>
+      <c r="E2" s="49">
+        <v>2019</v>
+      </c>
+      <c r="F2" s="49">
+        <v>2021</v>
+      </c>
+      <c r="G2" s="49">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="49">
+        <v>2024</v>
+      </c>
+      <c r="I2" s="61"/>
+    </row>
+    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A14" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A15" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13729FA8-C751-4019-ACB7-C1207E47EA7B}">
+  <dimension ref="B1:R8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="18" max="18" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2">
+        <v>2014</v>
+      </c>
+      <c r="F2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>2015</v>
+      </c>
+      <c r="F3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>2017</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="H4" s="45">
+        <v>210205</v>
+      </c>
+      <c r="I4" s="45">
+        <v>319318</v>
+      </c>
+      <c r="J4" s="45">
+        <v>288</v>
+      </c>
+      <c r="K4" s="45">
+        <v>50</v>
+      </c>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45">
+        <f>SUM(H4:L4)</f>
+        <v>529861</v>
+      </c>
+      <c r="R4" s="46">
+        <f>H4/M4</f>
+        <v>0.39671725226049853</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>2019</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="H5" s="45">
+        <v>203152</v>
+      </c>
+      <c r="I5" s="45">
+        <v>302075</v>
+      </c>
+      <c r="J5" s="45">
+        <v>215</v>
+      </c>
+      <c r="K5" s="45">
+        <v>1159</v>
+      </c>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45">
+        <f t="shared" ref="M5:M8" si="0">SUM(H5:L5)</f>
+        <v>506601</v>
+      </c>
+      <c r="R5" s="46">
+        <f t="shared" ref="R5:R8" si="1">H5/M5</f>
+        <v>0.40100986772627767</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>2021</v>
+      </c>
+      <c r="F6">
+        <v>44</v>
+      </c>
+      <c r="H6" s="45">
+        <v>223420</v>
+      </c>
+      <c r="I6" s="45">
+        <v>284397</v>
+      </c>
+      <c r="J6" s="45">
+        <v>1105</v>
+      </c>
+      <c r="K6" s="45">
+        <v>127</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45">
+        <f t="shared" si="0"/>
+        <v>509049</v>
+      </c>
+      <c r="R6" s="46">
+        <f t="shared" si="1"/>
+        <v>0.43889684490098202</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7">
+        <v>43</v>
+      </c>
+      <c r="H7" s="45">
+        <v>207167</v>
+      </c>
+      <c r="I7" s="45">
+        <v>271052</v>
+      </c>
+      <c r="J7" s="45">
+        <v>459</v>
+      </c>
+      <c r="K7" s="45">
+        <v>315</v>
+      </c>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45">
+        <f t="shared" si="0"/>
+        <v>478993</v>
+      </c>
+      <c r="R7" s="46">
+        <f t="shared" si="1"/>
+        <v>0.4325052766950665</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>2024</v>
+      </c>
+      <c r="F8">
+        <v>34</v>
+      </c>
+      <c r="H8" s="45">
+        <v>173494</v>
+      </c>
+      <c r="I8" s="45">
+        <v>332464</v>
+      </c>
+      <c r="J8" s="45">
+        <v>338</v>
+      </c>
+      <c r="K8" s="45">
+        <v>195</v>
+      </c>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45">
+        <f t="shared" si="0"/>
+        <v>506491</v>
+      </c>
+      <c r="R8" s="46">
+        <f t="shared" si="1"/>
+        <v>0.34254113103687922</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4B6226-F642-48D6-8B03-1A61B9F2366D}">
   <dimension ref="A2:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9594,44 +10365,44 @@
         <v>2023</v>
       </c>
       <c r="B7" s="18"/>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="64" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="52.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17"/>
       <c r="B8" s="18"/>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="64" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9665,44 +10436,44 @@
         <v>2024</v>
       </c>
       <c r="B11" s="18"/>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="64" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="54" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="47" t="s">
+      <c r="H12" s="64" t="s">
         <v>34</v>
       </c>
     </row>
@@ -9843,7 +10614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D0F07A-7E64-449D-92CE-EA1004D1ECCA}">
   <dimension ref="B2:J15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10176,7 +10947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085B938E-A436-4CE7-966F-A60A95C97A18}">
   <dimension ref="B1:F20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10187,31 +10958,31 @@
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:6" ht="50.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="19"/>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="65" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="50.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="19"/>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="65" t="s">
         <v>52</v>
       </c>
     </row>
@@ -10236,31 +11007,31 @@
     <row r="6" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="2:6" ht="37.200000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="19"/>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="66" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="37.200000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="19"/>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="66" t="s">
         <v>51</v>
       </c>
     </row>
@@ -10391,7 +11162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3FA2F6C-953C-4E43-B0A5-81F8E2354CB4}">
   <dimension ref="B2:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10680,7 +11451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{666AB2DB-7F68-407B-BB06-2027DF2491D4}">
   <dimension ref="B2:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10945,7 +11716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBF80E9-A514-4713-934C-E88142F3208D}">
   <dimension ref="B2:K18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
